--- a/lib/measures/ReportRetrofitEmbodiedCarbon/resources/optimization_updated.xlsx
+++ b/lib/measures/ReportRetrofitEmbodiedCarbon/resources/optimization_updated.xlsx
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>256.11</v>
+        <v>5471.82</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
